--- a/public/import-vzor.xlsx
+++ b/public/import-vzor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Názov</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Odporúčané</t>
   </si>
   <si>
+    <t>Obrázok</t>
+  </si>
+  <si>
     <t>Parametre</t>
   </si>
   <si>
@@ -85,6 +88,9 @@
     <t>áno</t>
   </si>
   <si>
+    <t>https://cdn.example.com/obrazky/wm-250.jpg</t>
+  </si>
+  <si>
     <t>Prúd:250 A;Napätie:230 V;Hmotnosť:8,5 kg</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>https://cdn.example.com/obrazky/wh-900.jpg</t>
+  </si>
+  <si>
     <t>Tienenie:DIN 4/9-13;Napájanie:solárne + batéria</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t>Kožené rukavice s predĺženým lemom pre bezpečnú manipuláciu.</t>
   </si>
   <si>
+    <t>https://cdn.example.com/obrazky/rukavice-pro.jpg</t>
+  </si>
+  <si>
     <t>Materiál:hovädzia koža;Veľkosť:10</t>
   </si>
   <si>
@@ -149,6 +161,9 @@
   </si>
   <si>
     <t>Na objednávku</t>
+  </si>
+  <si>
+    <t>https://cdn.example.com/obrazky/o2-10l.jpg</t>
   </si>
   <si>
     <t>Objem:10 l;Tlak:200 bar</t>
@@ -158,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +188,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -213,14 +235,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -513,13 +541,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="13" width="22.7109375" customWidth="1"/>
+    <col min="1" max="14" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,172 +587,190 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
         <v>429</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="M2">
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="I4" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4">
-        <v>12.5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5">
+        <v>31</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L2" r:id="rId1"/>
+    <hyperlink ref="L3" r:id="rId2"/>
+    <hyperlink ref="L4" r:id="rId3"/>
+    <hyperlink ref="L5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>